--- a/testdata/Scenario1_Output.xlsx
+++ b/testdata/Scenario1_Output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="13">
   <si>
     <t>Company Name</t>
   </si>
@@ -39,6 +39,18 @@
   </si>
   <si>
     <t>Insurance Company Name</t>
+  </si>
+  <si>
+    <t>Care Health</t>
+  </si>
+  <si>
+    <t>₹6,008</t>
+  </si>
+  <si>
+    <t>₹6,058</t>
+  </si>
+  <si>
+    <t>₹8,048</t>
   </si>
 </sst>
 </file>

--- a/testdata/Scenario1_Output.xlsx
+++ b/testdata/Scenario1_Output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="14">
   <si>
     <t>Company Name</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>₹8,048</t>
+  </si>
+  <si>
+    <t>₹2,156</t>
   </si>
 </sst>
 </file>
@@ -124,10 +127,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Scenario1_Output.xlsx
+++ b/testdata/Scenario1_Output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="14">
   <si>
     <t>Company Name</t>
   </si>
@@ -103,7 +103,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>4</v>

--- a/testdata/Scenario1_Output.xlsx
+++ b/testdata/Scenario1_Output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="14">
   <si>
     <t>Company Name</t>
   </si>

--- a/testdata/Scenario1_Output.xlsx
+++ b/testdata/Scenario1_Output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="14">
   <si>
     <t>Company Name</t>
   </si>
@@ -103,7 +103,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>4</v>

--- a/testdata/Scenario1_Output.xlsx
+++ b/testdata/Scenario1_Output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="14">
   <si>
     <t>Company Name</t>
   </si>
